--- a/doc_templates/tpl_pnl.xlsx
+++ b/doc_templates/tpl_pnl.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\2026년_프로젝트\P02.서비스\[2026.01.01]KICPA운영및개발\01.계약문서\2026_0320_[한공회]2026년03월분_콘텐츠개발계약(신규00)_조세지원본부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\P08.AI\04.한공회콘텐츠관리Tool\01.자료\정산자료 템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3C618C-16FB-469C-AB90-957B9B77BA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA893A34-4CD5-4325-8B93-61E807204454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="손익분석서_V1.0" sheetId="43" r:id="rId1"/>
@@ -229,7 +229,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>한국공인회계사 콘텐츠 개발(신규14차시)</t>
+    <t>한국공인회계사 콘텐츠 개발</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -864,6 +864,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="16" fillId="0" borderId="8" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="55" fontId="16" fillId="0" borderId="2" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="55" fontId="16" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -893,39 +926,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="16" fillId="0" borderId="8" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="55" fontId="16" fillId="0" borderId="2" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="55" fontId="16" fillId="0" borderId="9" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -1329,17 +1329,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
     </row>
     <row r="2" spans="1:10" ht="14.25">
       <c r="A2" s="1"/>
@@ -1362,12 +1362,12 @@
       <c r="E3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="104" t="s">
+      <c r="F3" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="106"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="96"/>
     </row>
     <row r="4" spans="1:10" s="23" customFormat="1" ht="14.25" customHeight="1">
       <c r="A4" s="37">
@@ -1379,12 +1379,10 @@
       <c r="E4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="107">
-        <v>46097</v>
-      </c>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="109"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="99"/>
     </row>
     <row r="5" spans="1:10" s="23" customFormat="1" ht="14.25" customHeight="1">
       <c r="A5" s="35"/>
@@ -1394,12 +1392,12 @@
       <c r="E5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="110" t="s">
+      <c r="F5" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="112"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="102"/>
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="38"/>
@@ -1413,40 +1411,40 @@
       <c r="I6" s="76"/>
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
       <c r="I7" s="77" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
       <c r="I8" s="78">
         <v>7000000</v>
       </c>
       <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="108" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="42" t="s">
@@ -1475,22 +1473,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A10" s="98"/>
+      <c r="A10" s="109"/>
       <c r="B10" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="28">
-        <v>46085</v>
-      </c>
-      <c r="E10" s="28">
-        <v>46108</v>
-      </c>
-      <c r="F10" s="29">
-        <v>0.05</v>
-      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="30" t="s">
         <v>33</v>
       </c>
@@ -1500,26 +1492,20 @@
       </c>
       <c r="I10" s="89">
         <f>(E10-D10)/30*F10*H10+1</f>
-        <v>339251.00000000006</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A11" s="98"/>
+      <c r="A11" s="109"/>
       <c r="B11" s="43" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="28">
-        <v>46085</v>
-      </c>
-      <c r="E11" s="28">
-        <v>46108</v>
-      </c>
-      <c r="F11" s="29">
-        <v>0.25</v>
-      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="30" t="s">
         <v>33</v>
       </c>
@@ -1529,11 +1515,11 @@
       </c>
       <c r="I11" s="89">
         <f>(E11-D11)/30*F11*H11+1</f>
-        <v>1696251</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A12" s="98"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="44"/>
@@ -1545,7 +1531,7 @@
       <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A13" s="98"/>
+      <c r="A13" s="109"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
       <c r="D13" s="44"/>
@@ -1556,7 +1542,7 @@
       <c r="I13" s="90"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A14" s="98"/>
+      <c r="A14" s="109"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
       <c r="D14" s="44"/>
@@ -1567,23 +1553,23 @@
       <c r="I14" s="90"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="99"/>
-      <c r="B15" s="92" t="s">
+      <c r="A15" s="110"/>
+      <c r="B15" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
       <c r="I15" s="81">
         <f>SUM(I10:I14)</f>
-        <v>2035502</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="111" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="42" t="s">
@@ -1612,7 +1598,7 @@
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="101"/>
+      <c r="A17" s="112"/>
       <c r="B17" s="49" t="s">
         <v>42</v>
       </c>
@@ -1623,7 +1609,7 @@
         <v>45000</v>
       </c>
       <c r="E17" s="50">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45" t="s">
@@ -1632,13 +1618,13 @@
       <c r="H17" s="52"/>
       <c r="I17" s="80">
         <f>(D17*E17)</f>
-        <v>1350000</v>
+        <v>0</v>
       </c>
       <c r="J17" s="71"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="101"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="49"/>
       <c r="C18" s="50"/>
       <c r="D18" s="48"/>
@@ -1654,7 +1640,7 @@
       <c r="K18" s="22"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="101"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="49"/>
       <c r="C19" s="50"/>
       <c r="D19" s="48"/>
@@ -1666,7 +1652,7 @@
       <c r="J19" s="22"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="101"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="43"/>
       <c r="C20" s="50"/>
       <c r="D20" s="48"/>
@@ -1678,7 +1664,7 @@
       <c r="J20" s="22"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="101"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="43"/>
       <c r="C21" s="50"/>
       <c r="D21" s="48"/>
@@ -1691,7 +1677,7 @@
       <c r="K21" s="26"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="101"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="54"/>
       <c r="C22" s="50"/>
       <c r="D22" s="48"/>
@@ -1704,7 +1690,7 @@
       <c r="K22" s="26"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="101"/>
+      <c r="A23" s="112"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
       <c r="D23" s="32"/>
@@ -1717,18 +1703,18 @@
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="59"/>
-      <c r="B24" s="92" t="s">
+      <c r="B24" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
       <c r="I24" s="83">
         <f>SUM(I17:I23)</f>
-        <v>1350000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
@@ -1744,7 +1730,7 @@
       </c>
       <c r="I25" s="84">
         <f>SUM(I15,I24)</f>
-        <v>3385502</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
@@ -1760,7 +1746,7 @@
       </c>
       <c r="I26" s="65">
         <f>I24/I8</f>
-        <v>0.19285714285714287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
@@ -1776,7 +1762,7 @@
       </c>
       <c r="I27" s="67">
         <f>I8-I25</f>
-        <v>3614498</v>
+        <v>6999998</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
@@ -1792,7 +1778,7 @@
       </c>
       <c r="I28" s="69">
         <f>I27/I8</f>
-        <v>0.51635685714285717</v>
+        <v>0.99999971428571433</v>
       </c>
       <c r="J28" s="22"/>
     </row>
@@ -1850,7 +1836,7 @@
       </c>
       <c r="D32" s="70">
         <f>SUMIF(G10:G23,"SS",I10:I23)</f>
-        <v>3385502</v>
+        <v>2</v>
       </c>
       <c r="E32" s="73">
         <v>8850000</v>
@@ -1871,7 +1857,7 @@
       </c>
       <c r="D33" s="20">
         <f>SUM(D32:D32)</f>
-        <v>3385502</v>
+        <v>2</v>
       </c>
       <c r="E33" s="20">
         <f>SUM(E32:E32)</f>
@@ -1895,18 +1881,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A16:A23"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="F5:I5"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A16:A23"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.46" right="0.56000000000000005" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
